--- a/data/lab-analyses_raw-data/2021-11-17_DetroitRiver_lab-analyses.xlsx
+++ b/data/lab-analyses_raw-data/2021-11-17_DetroitRiver_lab-analyses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trentu-my.sharepoint.com/personal/sandraklemet_trentu_ca/Documents/Documents/Etudes/Trent/Xenopoulos lab/Projects/LakeErie_animal-excretion/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trentu-my.sharepoint.com/personal/sandraklemet_trentu_ca/Documents/Documents/Etudes/Trent/Xenopoulos lab/Projects/LakeErie_animal-excretion/data/lab-analyses_raw-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="399" documentId="13_ncr:1_{7C8BF3FC-06BC-4E3E-A3F0-E9F8B77F733C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{683B5B6D-BDDD-4A96-9B48-345006B06044}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{C52185F6-50D3-4B58-B3B1-F9E06922E42E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{C52185F6-50D3-4B58-B3B1-F9E06922E42E}"/>
   </bookViews>
   <sheets>
     <sheet name="SRP STD curve" sheetId="1" r:id="rId1"/>
@@ -197,10 +197,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -504,6 +503,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -511,7 +511,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -841,6 +840,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -848,7 +848,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1200,6 +1199,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1207,7 +1207,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1527,6 +1526,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1534,7 +1534,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1864,6 +1863,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1871,7 +1871,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2201,6 +2200,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2208,7 +2208,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2538,6 +2537,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2545,7 +2545,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2875,6 +2874,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2882,7 +2882,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3212,6 +3211,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3219,7 +3219,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3549,6 +3548,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3556,7 +3556,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3886,6 +3885,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3893,7 +3893,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10477,9 +10476,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -10517,7 +10516,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -10623,7 +10622,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -10765,7 +10764,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -17688,15 +17687,15 @@
       <c r="C2">
         <v>2.9899999999999999E-2</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>2.9100000000000001E-2</v>
       </c>
       <c r="E2">
-        <f>AVERAGE(C2:D2)</f>
+        <f t="shared" ref="E2:E33" si="0">AVERAGE(C2:D2)</f>
         <v>2.9499999999999998E-2</v>
       </c>
       <c r="F2">
-        <f>E2*$L$1+$L$2</f>
+        <f t="shared" ref="F2:F33" si="1">E2*$L$1+$L$2</f>
         <v>30.952946323827376</v>
       </c>
       <c r="K2" t="s">
@@ -17720,11 +17719,11 @@
         <v>1.95E-2</v>
       </c>
       <c r="E3">
-        <f>AVERAGE(C3:D3)</f>
+        <f t="shared" si="0"/>
         <v>1.8950000000000002E-2</v>
       </c>
       <c r="F3">
-        <f>E3*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>20.930643997385719</v>
       </c>
     </row>
@@ -17738,15 +17737,15 @@
       <c r="C4">
         <v>1.9699999999999999E-2</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>1.54E-2</v>
       </c>
       <c r="E4">
-        <f>AVERAGE(C4:D4)</f>
+        <f t="shared" si="0"/>
         <v>1.755E-2</v>
       </c>
       <c r="F4">
-        <f>E4*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>19.600670228947958</v>
       </c>
     </row>
@@ -17760,15 +17759,15 @@
       <c r="C5" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>2.1899999999999999E-2</v>
       </c>
       <c r="E5">
-        <f>AVERAGE(C5:D5)</f>
+        <f t="shared" si="0"/>
         <v>1.495E-2</v>
       </c>
       <c r="F5">
-        <f>E5*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>17.130718944706413</v>
       </c>
     </row>
@@ -17782,15 +17781,15 @@
       <c r="C6">
         <v>1.4800000000000001E-2</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>1.4E-2</v>
       </c>
       <c r="E6">
-        <f>AVERAGE(C6:D6)</f>
+        <f t="shared" si="0"/>
         <v>1.44E-2</v>
       </c>
       <c r="F6">
-        <f>E6*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>16.60822924996301</v>
       </c>
     </row>
@@ -17804,15 +17803,15 @@
       <c r="C7">
         <v>1.32E-2</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="E7">
-        <f>AVERAGE(C7:D7)</f>
+        <f t="shared" si="0"/>
         <v>9.6000000000000009E-3</v>
       </c>
       <c r="F7">
-        <f>E7*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>12.048319186747847</v>
       </c>
     </row>
@@ -17826,15 +17825,15 @@
       <c r="C8">
         <v>1.37E-2</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>0.02</v>
       </c>
       <c r="E8">
-        <f>AVERAGE(C8:D8)</f>
+        <f t="shared" si="0"/>
         <v>1.685E-2</v>
       </c>
       <c r="F8">
-        <f>E8*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>18.935683344729082</v>
       </c>
     </row>
@@ -17848,15 +17847,15 @@
       <c r="C9">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>2.12E-2</v>
       </c>
       <c r="E9">
-        <f>AVERAGE(C9:D9)</f>
+        <f t="shared" si="0"/>
         <v>2.1100000000000001E-2</v>
       </c>
       <c r="F9">
-        <f>E9*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>22.973103713200842</v>
       </c>
     </row>
@@ -17870,15 +17869,15 @@
       <c r="C10">
         <v>2.7400000000000001E-2</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="E10">
-        <f>AVERAGE(C10:D10)</f>
+        <f t="shared" si="0"/>
         <v>2.47E-2</v>
       </c>
       <c r="F10">
-        <f>E10*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>26.393036260612213</v>
       </c>
     </row>
@@ -17892,15 +17891,15 @@
       <c r="C11">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>3.32E-2</v>
       </c>
       <c r="E11">
-        <f>AVERAGE(C11:D11)</f>
+        <f t="shared" si="0"/>
         <v>3.8099999999999995E-2</v>
       </c>
       <c r="F11">
-        <f>E11*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>39.122785187087871</v>
       </c>
     </row>
@@ -17914,15 +17913,15 @@
       <c r="C12">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>2.6700000000000002E-2</v>
       </c>
       <c r="E12">
-        <f>AVERAGE(C12:D12)</f>
+        <f t="shared" si="0"/>
         <v>3.005E-2</v>
       </c>
       <c r="F12">
-        <f>E12*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>31.475436018570782</v>
       </c>
     </row>
@@ -17936,15 +17935,15 @@
       <c r="C13">
         <v>2.7900000000000001E-2</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>3.85E-2</v>
       </c>
       <c r="E13">
-        <f>AVERAGE(C13:D13)</f>
+        <f t="shared" si="0"/>
         <v>3.32E-2</v>
       </c>
       <c r="F13">
-        <f>E13*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>34.467876997555734</v>
       </c>
     </row>
@@ -17962,11 +17961,11 @@
         <v>2.64E-2</v>
       </c>
       <c r="E14">
-        <f>AVERAGE(C14:D14)</f>
+        <f t="shared" si="0"/>
         <v>2.6000000000000002E-2</v>
       </c>
       <c r="F14">
-        <f>E14*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>27.62801190273299</v>
       </c>
     </row>
@@ -17984,11 +17983,11 @@
         <v>2.7699999999999999E-2</v>
       </c>
       <c r="E15">
-        <f>AVERAGE(C15:D15)</f>
+        <f t="shared" si="0"/>
         <v>2.4649999999999998E-2</v>
       </c>
       <c r="F15">
-        <f>E15*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>26.345537197453719</v>
       </c>
     </row>
@@ -18006,11 +18005,11 @@
         <v>1.8800000000000001E-2</v>
       </c>
       <c r="E16">
-        <f>AVERAGE(C16:D16)</f>
+        <f t="shared" si="0"/>
         <v>1.7600000000000001E-2</v>
       </c>
       <c r="F16">
-        <f>E16*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>19.648169292106452</v>
       </c>
     </row>
@@ -18028,11 +18027,11 @@
         <v>1.5699999999999999E-2</v>
       </c>
       <c r="E17">
-        <f>AVERAGE(C17:D17)</f>
+        <f t="shared" si="0"/>
         <v>1.38E-2</v>
       </c>
       <c r="F17">
-        <f>E17*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>16.038240492061114</v>
       </c>
     </row>
@@ -18050,11 +18049,11 @@
         <v>1.23E-2</v>
       </c>
       <c r="E18">
-        <f>AVERAGE(C18:D18)</f>
+        <f t="shared" si="0"/>
         <v>1.35E-2</v>
       </c>
       <c r="F18">
-        <f>E18*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>15.753246113110166</v>
       </c>
     </row>
@@ -18068,15 +18067,15 @@
       <c r="C19">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="E19">
-        <f>AVERAGE(C19:D19)</f>
+        <f t="shared" si="0"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="F19">
-        <f>E19*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>20.028161797374381</v>
       </c>
     </row>
@@ -18094,11 +18093,11 @@
         <v>1.29E-2</v>
       </c>
       <c r="E20">
-        <f>AVERAGE(C20:D20)</f>
+        <f t="shared" si="0"/>
         <v>1.3100000000000001E-2</v>
       </c>
       <c r="F20">
-        <f>E20*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>15.373253607842237</v>
       </c>
     </row>
@@ -18116,11 +18115,11 @@
         <v>0.1216</v>
       </c>
       <c r="E21">
-        <f>AVERAGE(C21:D21)</f>
+        <f t="shared" si="0"/>
         <v>0.12490000000000001</v>
       </c>
       <c r="F21">
-        <f>E21*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>121.58115883022876</v>
       </c>
     </row>
@@ -18134,15 +18133,15 @@
       <c r="C22">
         <v>5.16E-2</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
         <v>5.7299999999999997E-2</v>
       </c>
       <c r="E22">
-        <f>AVERAGE(C22:D22)</f>
+        <f t="shared" si="0"/>
         <v>5.4449999999999998E-2</v>
       </c>
       <c r="F22">
-        <f>E22*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>54.654978839914527</v>
       </c>
     </row>
@@ -18156,15 +18155,15 @@
       <c r="C23">
         <v>4.7100000000000003E-2</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="2">
         <v>4.9599999999999998E-2</v>
       </c>
       <c r="E23">
-        <f>AVERAGE(C23:D23)</f>
+        <f t="shared" si="0"/>
         <v>4.8350000000000004E-2</v>
       </c>
       <c r="F23">
-        <f>E23*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>48.860093134578591</v>
       </c>
     </row>
@@ -18182,11 +18181,11 @@
         <v>3.9899999999999998E-2</v>
       </c>
       <c r="E24">
-        <f>AVERAGE(C24:D24)</f>
+        <f t="shared" si="0"/>
         <v>3.8900000000000004E-2</v>
       </c>
       <c r="F24">
-        <f>E24*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>39.882770197623742</v>
       </c>
     </row>
@@ -18200,15 +18199,15 @@
       <c r="C25">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="2">
         <v>2.3800000000000002E-2</v>
       </c>
       <c r="E25">
-        <f>AVERAGE(C25:D25)</f>
+        <f t="shared" si="0"/>
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="F25">
-        <f>E25*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>23.353096218468771</v>
       </c>
     </row>
@@ -18222,15 +18221,15 @@
       <c r="C26">
         <v>4.2099999999999999E-2</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="2">
         <v>4.3700000000000003E-2</v>
       </c>
       <c r="E26">
-        <f>AVERAGE(C26:D26)</f>
+        <f t="shared" si="0"/>
         <v>4.2900000000000001E-2</v>
       </c>
       <c r="F26">
-        <f>E26*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>43.682695250303041</v>
       </c>
     </row>
@@ -18248,11 +18247,11 @@
         <v>3.8199999999999998E-2</v>
       </c>
       <c r="E27">
-        <f>AVERAGE(C27:D27)</f>
+        <f t="shared" si="0"/>
         <v>4.0849999999999997E-2</v>
       </c>
       <c r="F27">
-        <f>E27*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>41.735233660804894</v>
       </c>
     </row>
@@ -18266,15 +18265,15 @@
       <c r="C28">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="2">
         <v>1.8100000000000002E-2</v>
       </c>
       <c r="E28">
-        <f>AVERAGE(C28:D28)</f>
+        <f t="shared" si="0"/>
         <v>2.0900000000000002E-2</v>
       </c>
       <c r="F28">
-        <f>E28*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>22.783107460566878</v>
       </c>
     </row>
@@ -18292,11 +18291,11 @@
         <v>2.3900000000000001E-2</v>
       </c>
       <c r="E29">
-        <f>AVERAGE(C29:D29)</f>
+        <f t="shared" si="0"/>
         <v>2.4E-2</v>
       </c>
       <c r="F29">
-        <f>E29*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>25.728049376393336</v>
       </c>
     </row>
@@ -18310,15 +18309,15 @@
       <c r="C30">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="2">
         <v>3.9100000000000003E-2</v>
       </c>
       <c r="E30">
-        <f>AVERAGE(C30:D30)</f>
+        <f t="shared" si="0"/>
         <v>3.9150000000000004E-2</v>
       </c>
       <c r="F30">
-        <f>E30*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>40.1202655134162</v>
       </c>
     </row>
@@ -18336,11 +18335,11 @@
         <v>3.4799999999999998E-2</v>
       </c>
       <c r="E31">
-        <f>AVERAGE(C31:D31)</f>
+        <f t="shared" si="0"/>
         <v>3.5400000000000001E-2</v>
       </c>
       <c r="F31">
-        <f>E31*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>36.557835776529352</v>
       </c>
     </row>
@@ -18358,11 +18357,11 @@
         <v>3.1399999999999997E-2</v>
       </c>
       <c r="E32">
-        <f>AVERAGE(C32:D32)</f>
+        <f t="shared" si="0"/>
         <v>2.665E-2</v>
       </c>
       <c r="F32">
-        <f>E32*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>28.245499723793372</v>
       </c>
     </row>
@@ -18376,15 +18375,15 @@
       <c r="C33">
         <v>2.58E-2</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="2">
         <v>2.8199999999999999E-2</v>
       </c>
       <c r="E33">
-        <f>AVERAGE(C33:D33)</f>
+        <f t="shared" si="0"/>
         <v>2.7E-2</v>
       </c>
       <c r="F33">
-        <f>E33*$L$1+$L$2</f>
+        <f t="shared" si="1"/>
         <v>28.577993165902811</v>
       </c>
     </row>
@@ -18402,11 +18401,11 @@
         <v>2.2200000000000001E-2</v>
       </c>
       <c r="E34">
-        <f>AVERAGE(C34:D34)</f>
+        <f t="shared" ref="E34:E65" si="2">AVERAGE(C34:D34)</f>
         <v>0.02</v>
       </c>
       <c r="F34">
-        <f>E34*$L$1+$L$2</f>
+        <f t="shared" ref="F34:F65" si="3">E34*$L$1+$L$2</f>
         <v>21.928124323714034</v>
       </c>
     </row>
@@ -18424,11 +18423,11 @@
         <v>1.49E-2</v>
       </c>
       <c r="E35">
-        <f>AVERAGE(C35:D35)</f>
+        <f t="shared" si="2"/>
         <v>1.465E-2</v>
       </c>
       <c r="F35">
-        <f>E35*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>16.845724565755468</v>
       </c>
     </row>
@@ -18442,15 +18441,15 @@
       <c r="C36">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="2">
         <v>2.53E-2</v>
       </c>
       <c r="E36">
-        <f>AVERAGE(C36:D36)</f>
+        <f t="shared" si="2"/>
         <v>2.7049999999999998E-2</v>
       </c>
       <c r="F36">
-        <f>E36*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>28.625492229061301</v>
       </c>
     </row>
@@ -18468,11 +18467,11 @@
         <v>2.0799999999999999E-2</v>
       </c>
       <c r="E37">
-        <f>AVERAGE(C37:D37)</f>
+        <f t="shared" si="2"/>
         <v>2.3550000000000001E-2</v>
       </c>
       <c r="F37">
-        <f>E37*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>25.300557807966914</v>
       </c>
     </row>
@@ -18486,15 +18485,15 @@
       <c r="C38">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="2">
         <v>2.87E-2</v>
       </c>
       <c r="E38">
-        <f>AVERAGE(C38:D38)</f>
+        <f t="shared" si="2"/>
         <v>2.2850000000000002E-2</v>
       </c>
       <c r="F38">
-        <f>E38*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>24.635570923748038</v>
       </c>
     </row>
@@ -18508,15 +18507,15 @@
       <c r="C39">
         <v>1.52E-2</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="2">
         <v>1.9300000000000001E-2</v>
       </c>
       <c r="E39">
-        <f>AVERAGE(C39:D39)</f>
+        <f t="shared" si="2"/>
         <v>1.7250000000000001E-2</v>
       </c>
       <c r="F39">
-        <f>E39*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>19.315675849997014</v>
       </c>
     </row>
@@ -18530,15 +18529,15 @@
       <c r="C40">
         <v>2.6100000000000002E-2</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="2">
         <v>2.46E-2</v>
       </c>
       <c r="E40">
-        <f>AVERAGE(C40:D40)</f>
+        <f t="shared" si="2"/>
         <v>2.5350000000000001E-2</v>
       </c>
       <c r="F40">
-        <f>E40*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>27.0105240816726</v>
       </c>
     </row>
@@ -18556,11 +18555,11 @@
         <v>1.8599999999999998E-2</v>
       </c>
       <c r="E41">
-        <f>AVERAGE(C41:D41)</f>
+        <f t="shared" si="2"/>
         <v>1.3999999999999999E-2</v>
       </c>
       <c r="F41">
-        <f>E41*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>16.228236744695078</v>
       </c>
     </row>
@@ -18578,11 +18577,11 @@
         <v>1.8100000000000002E-2</v>
       </c>
       <c r="E42">
-        <f>AVERAGE(C42:D42)</f>
+        <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
       <c r="F42">
-        <f>E42*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>21.928124323714034</v>
       </c>
     </row>
@@ -18596,15 +18595,15 @@
       <c r="C43">
         <v>3.1899999999999998E-2</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="2">
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="E43">
-        <f>AVERAGE(C43:D43)</f>
+        <f t="shared" si="2"/>
         <v>3.1600000000000003E-2</v>
       </c>
       <c r="F43">
-        <f>E43*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>32.947906976484013</v>
       </c>
     </row>
@@ -18618,15 +18617,15 @@
       <c r="C44">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="2">
         <v>1.4200000000000001E-2</v>
       </c>
       <c r="E44">
-        <f>AVERAGE(C44:D44)</f>
+        <f t="shared" si="2"/>
         <v>1.6899999999999998E-2</v>
       </c>
       <c r="F44">
-        <f>E44*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>18.983182407887572</v>
       </c>
     </row>
@@ -18640,15 +18639,15 @@
       <c r="C45">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="2">
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="E45">
-        <f>AVERAGE(C45:D45)</f>
+        <f t="shared" si="2"/>
         <v>2.5750000000000002E-2</v>
       </c>
       <c r="F45">
-        <f>E45*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>27.390516586940532</v>
       </c>
     </row>
@@ -18666,11 +18665,11 @@
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="E46">
-        <f>AVERAGE(C46:D46)</f>
+        <f t="shared" si="2"/>
         <v>1.9599999999999999E-2</v>
       </c>
       <c r="F46">
-        <f>E46*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>21.548131818446102</v>
       </c>
     </row>
@@ -18688,11 +18687,11 @@
         <v>3.5400000000000001E-2</v>
       </c>
       <c r="E47">
-        <f>AVERAGE(C47:D47)</f>
+        <f t="shared" si="2"/>
         <v>3.5650000000000001E-2</v>
       </c>
       <c r="F47">
-        <f>E47*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>36.795331092321803</v>
       </c>
     </row>
@@ -18710,11 +18709,11 @@
         <v>4.3299999999999998E-2</v>
       </c>
       <c r="E48">
-        <f>AVERAGE(C48:D48)</f>
+        <f t="shared" si="2"/>
         <v>4.48E-2</v>
       </c>
       <c r="F48">
-        <f>E48*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>45.48765965032571</v>
       </c>
     </row>
@@ -18732,11 +18731,11 @@
         <v>3.2399999999999998E-2</v>
       </c>
       <c r="E49">
-        <f>AVERAGE(C49:D49)</f>
+        <f t="shared" si="2"/>
         <v>2.7949999999999999E-2</v>
       </c>
       <c r="F49">
-        <f>E49*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>29.480475365914145</v>
       </c>
     </row>
@@ -18754,11 +18753,11 @@
         <v>2.12E-2</v>
       </c>
       <c r="E50">
-        <f>AVERAGE(C50:D50)</f>
+        <f t="shared" si="2"/>
         <v>2.155E-2</v>
       </c>
       <c r="F50">
-        <f>E50*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>23.400595281627261</v>
       </c>
     </row>
@@ -18776,11 +18775,11 @@
         <v>2.5399999999999999E-2</v>
       </c>
       <c r="E51">
-        <f>AVERAGE(C51:D51)</f>
+        <f t="shared" si="2"/>
         <v>2.9149999999999999E-2</v>
       </c>
       <c r="F51">
-        <f>E51*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>30.620452881717938</v>
       </c>
     </row>
@@ -18794,15 +18793,15 @@
       <c r="C52">
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="2">
         <v>3.8100000000000002E-2</v>
       </c>
       <c r="E52">
-        <f>AVERAGE(C52:D52)</f>
+        <f t="shared" si="2"/>
         <v>3.6900000000000002E-2</v>
       </c>
       <c r="F52">
-        <f>E52*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>37.982807671284085</v>
       </c>
     </row>
@@ -18816,15 +18815,15 @@
       <c r="C53">
         <v>3.5400000000000001E-2</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="2">
         <v>3.1800000000000002E-2</v>
       </c>
       <c r="E53">
-        <f>AVERAGE(C53:D53)</f>
+        <f t="shared" si="2"/>
         <v>3.3600000000000005E-2</v>
       </c>
       <c r="F53">
-        <f>E53*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>34.84786950282367</v>
       </c>
     </row>
@@ -18838,15 +18837,15 @@
       <c r="C54">
         <v>3.8899999999999997E-2</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="2">
         <v>4.0399999999999998E-2</v>
       </c>
       <c r="E54">
-        <f>AVERAGE(C54:D54)</f>
+        <f t="shared" si="2"/>
         <v>3.9649999999999998E-2</v>
       </c>
       <c r="F54">
-        <f>E54*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>40.595256145001102</v>
       </c>
     </row>
@@ -18860,15 +18859,15 @@
       <c r="C55">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="2">
         <v>2.64E-2</v>
       </c>
       <c r="E55">
-        <f>AVERAGE(C55:D55)</f>
+        <f t="shared" si="2"/>
         <v>2.7700000000000002E-2</v>
       </c>
       <c r="F55">
-        <f>E55*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>29.242980050121691</v>
       </c>
     </row>
@@ -18886,11 +18885,11 @@
         <v>3.0599999999999999E-2</v>
       </c>
       <c r="E56">
-        <f>AVERAGE(C56:D56)</f>
+        <f t="shared" si="2"/>
         <v>2.895E-2</v>
       </c>
       <c r="F56">
-        <f>E56*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>30.430456629083974</v>
       </c>
     </row>
@@ -18904,15 +18903,15 @@
       <c r="C57">
         <v>2.2499999999999999E-2</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="2">
         <v>2.75E-2</v>
       </c>
       <c r="E57">
-        <f>AVERAGE(C57:D57)</f>
+        <f t="shared" si="2"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="F57">
-        <f>E57*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>26.678030639563161</v>
       </c>
     </row>
@@ -18926,15 +18925,15 @@
       <c r="C58">
         <v>3.2300000000000002E-2</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="2">
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="E58">
-        <f>AVERAGE(C58:D58)</f>
+        <f t="shared" si="2"/>
         <v>3.1800000000000002E-2</v>
       </c>
       <c r="F58">
-        <f>E58*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>33.137903229117981</v>
       </c>
     </row>
@@ -18952,11 +18951,11 @@
         <v>1.67E-2</v>
       </c>
       <c r="E59">
-        <f>AVERAGE(C59:D59)</f>
+        <f t="shared" si="2"/>
         <v>1.145E-2</v>
       </c>
       <c r="F59">
-        <f>E59*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>13.805784523612024</v>
       </c>
     </row>
@@ -18970,15 +18969,15 @@
       <c r="C60">
         <v>4.5900000000000003E-2</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="2">
         <v>4.0800000000000003E-2</v>
       </c>
       <c r="E60">
-        <f>AVERAGE(C60:D60)</f>
+        <f t="shared" si="2"/>
         <v>4.335E-2</v>
       </c>
       <c r="F60">
-        <f>E60*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>44.11018681872946</v>
       </c>
     </row>
@@ -18996,11 +18995,11 @@
         <v>2.52E-2</v>
       </c>
       <c r="E61">
-        <f>AVERAGE(C61:D61)</f>
+        <f t="shared" si="2"/>
         <v>2.53E-2</v>
       </c>
       <c r="F61">
-        <f>E61*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>26.963025018514109</v>
       </c>
     </row>
@@ -19018,11 +19017,11 @@
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="E62">
-        <f>AVERAGE(C62:D62)</f>
+        <f t="shared" si="2"/>
         <v>2.1600000000000001E-2</v>
       </c>
       <c r="F62">
-        <f>E62*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>23.448094344785755</v>
       </c>
     </row>
@@ -19040,11 +19039,11 @@
         <v>2.1600000000000001E-2</v>
       </c>
       <c r="E63">
-        <f>AVERAGE(C63:D63)</f>
+        <f t="shared" si="2"/>
         <v>2.2200000000000001E-2</v>
       </c>
       <c r="F63">
-        <f>E63*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>24.018083102687651</v>
       </c>
     </row>
@@ -19058,15 +19057,15 @@
       <c r="C64">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="2">
         <v>2.58E-2</v>
       </c>
       <c r="E64">
-        <f>AVERAGE(C64:D64)</f>
+        <f t="shared" si="2"/>
         <v>1.8149999999999999E-2</v>
       </c>
       <c r="F64">
-        <f>E64*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>20.170658986849855</v>
       </c>
     </row>
@@ -19084,11 +19083,11 @@
         <v>2.35E-2</v>
       </c>
       <c r="E65">
-        <f>AVERAGE(C65:D65)</f>
+        <f t="shared" si="2"/>
         <v>3.1600000000000003E-2</v>
       </c>
       <c r="F65">
-        <f>E65*$L$1+$L$2</f>
+        <f t="shared" si="3"/>
         <v>32.947906976484013</v>
       </c>
     </row>
@@ -19102,15 +19101,15 @@
       <c r="C66">
         <v>3.5400000000000001E-2</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="2">
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="E66">
-        <f>AVERAGE(C66:D66)</f>
+        <f t="shared" ref="E66:E97" si="4">AVERAGE(C66:D66)</f>
         <v>3.8199999999999998E-2</v>
       </c>
       <c r="F66">
-        <f>E66*$L$1+$L$2</f>
+        <f t="shared" ref="F66:F97" si="5">E66*$L$1+$L$2</f>
         <v>39.217783313404858</v>
       </c>
     </row>
@@ -19128,11 +19127,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="E67">
-        <f>AVERAGE(C67:D67)</f>
+        <f t="shared" si="4"/>
         <v>3.78E-2</v>
       </c>
       <c r="F67">
-        <f>E67*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>38.83779080813693</v>
       </c>
     </row>
@@ -19150,11 +19149,11 @@
         <v>0.02</v>
       </c>
       <c r="E68">
-        <f>AVERAGE(C68:D68)</f>
+        <f t="shared" si="4"/>
         <v>1.6300000000000002E-2</v>
       </c>
       <c r="F68">
-        <f>E68*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>18.413193649985679</v>
       </c>
     </row>
@@ -19172,11 +19171,11 @@
         <v>0.3619</v>
       </c>
       <c r="E69">
-        <f>AVERAGE(C69:D69)</f>
+        <f t="shared" si="4"/>
         <v>0.36560000000000004</v>
       </c>
       <c r="F69">
-        <f>E69*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>350.24164887520578</v>
       </c>
     </row>
@@ -19194,11 +19193,11 @@
         <v>0.1885</v>
       </c>
       <c r="E70">
-        <f>AVERAGE(C70:D70)</f>
+        <f t="shared" si="4"/>
         <v>0.18964999999999999</v>
       </c>
       <c r="F70">
-        <f>E70*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>183.09244562047496</v>
       </c>
     </row>
@@ -19216,11 +19215,11 @@
         <v>0.24629999999999999</v>
       </c>
       <c r="E71">
-        <f>AVERAGE(C71:D71)</f>
+        <f t="shared" si="4"/>
         <v>0.24809999999999999</v>
       </c>
       <c r="F71">
-        <f>E71*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>238.61885045275125</v>
       </c>
     </row>
@@ -19238,11 +19237,11 @@
         <v>0.1893</v>
       </c>
       <c r="E72">
-        <f>AVERAGE(C72:D72)</f>
+        <f t="shared" si="4"/>
         <v>0.1827</v>
       </c>
       <c r="F72">
-        <f>E72*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>176.49007584144465</v>
       </c>
     </row>
@@ -19256,15 +19255,15 @@
       <c r="C73">
         <v>7.9699999999999993E-2</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="2">
         <v>7.9200000000000007E-2</v>
       </c>
       <c r="E73">
-        <f>AVERAGE(C73:D73)</f>
+        <f t="shared" si="4"/>
         <v>7.9449999999999993E-2</v>
       </c>
       <c r="F73">
-        <f>E73*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>78.404510419160161</v>
       </c>
     </row>
@@ -19282,11 +19281,11 @@
         <v>0.2316</v>
       </c>
       <c r="E74">
-        <f>AVERAGE(C74:D74)</f>
+        <f t="shared" si="4"/>
         <v>0.22939999999999999</v>
       </c>
       <c r="F74">
-        <f>E74*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>220.85420083147551</v>
       </c>
     </row>
@@ -19300,15 +19299,15 @@
       <c r="C75">
         <v>0.24329999999999999</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75" s="2">
         <v>0.24079999999999999</v>
       </c>
       <c r="E75">
-        <f>AVERAGE(C75:D75)</f>
+        <f t="shared" si="4"/>
         <v>0.24204999999999999</v>
       </c>
       <c r="F75">
-        <f>E75*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>232.8714638105738</v>
       </c>
     </row>
@@ -19326,11 +19325,11 @@
         <v>0.3392</v>
       </c>
       <c r="E76">
-        <f>AVERAGE(C76:D76)</f>
+        <f t="shared" si="4"/>
         <v>0.33440000000000003</v>
       </c>
       <c r="F76">
-        <f>E76*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>320.60223346430723</v>
       </c>
     </row>
@@ -19348,11 +19347,11 @@
         <v>0.25540000000000002</v>
       </c>
       <c r="E77">
-        <f>AVERAGE(C77:D77)</f>
+        <f t="shared" si="4"/>
         <v>0.25390000000000001</v>
       </c>
       <c r="F77">
-        <f>E77*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>244.12874177913625</v>
       </c>
     </row>
@@ -19366,15 +19365,15 @@
       <c r="C78">
         <v>0.1721</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="2">
         <v>0.17269999999999999</v>
       </c>
       <c r="E78">
-        <f>AVERAGE(C78:D78)</f>
+        <f t="shared" si="4"/>
         <v>0.1724</v>
       </c>
       <c r="F78">
-        <f>E78*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>166.70526883079543</v>
       </c>
     </row>
@@ -19392,11 +19391,11 @@
         <v>0.15260000000000001</v>
       </c>
       <c r="E79">
-        <f>AVERAGE(C79:D79)</f>
+        <f t="shared" si="4"/>
         <v>0.15160000000000001</v>
       </c>
       <c r="F79">
-        <f>E79*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>146.94565855686312</v>
       </c>
     </row>
@@ -19414,11 +19413,11 @@
         <v>0.21229999999999999</v>
       </c>
       <c r="E80">
-        <f>AVERAGE(C80:D80)</f>
+        <f t="shared" si="4"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="F80">
-        <f>E80*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>205.27450811549039</v>
       </c>
     </row>
@@ -19436,11 +19435,11 @@
         <v>0.26979999999999998</v>
       </c>
       <c r="E81">
-        <f>AVERAGE(C81:D81)</f>
+        <f t="shared" si="4"/>
         <v>0.27539999999999998</v>
       </c>
       <c r="F81">
-        <f>E81*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>264.55333893728749</v>
       </c>
     </row>
@@ -19454,15 +19453,15 @@
       <c r="C82">
         <v>0.23400000000000001</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="2">
         <v>0.23469999999999999</v>
       </c>
       <c r="E82">
-        <f>AVERAGE(C82:D82)</f>
+        <f t="shared" si="4"/>
         <v>0.23435</v>
       </c>
       <c r="F82">
-        <f>E82*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>225.55660808416616</v>
       </c>
     </row>
@@ -19484,7 +19483,7 @@
         <v>0.28510000000000002</v>
       </c>
       <c r="F83">
-        <f>E83*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>273.7681571900348</v>
       </c>
     </row>
@@ -19498,15 +19497,15 @@
       <c r="C84">
         <v>0.19839999999999999</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84" s="2">
         <v>0.19420000000000001</v>
       </c>
       <c r="E84">
-        <f>AVERAGE(C84:D84)</f>
+        <f t="shared" ref="E84:E113" si="6">AVERAGE(C84:D84)</f>
         <v>0.1963</v>
       </c>
       <c r="F84">
-        <f>E84*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>189.40982102055432</v>
       </c>
     </row>
@@ -19524,11 +19523,11 @@
         <v>0.23180000000000001</v>
       </c>
       <c r="E85">
-        <f>AVERAGE(C85:D85)</f>
+        <f t="shared" si="6"/>
         <v>0.22794999999999999</v>
       </c>
       <c r="F85">
-        <f>E85*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>219.47672799987924</v>
       </c>
     </row>
@@ -19546,11 +19545,11 @@
         <v>0.1472</v>
       </c>
       <c r="E86">
-        <f>AVERAGE(C86:D86)</f>
+        <f t="shared" si="6"/>
         <v>0.14560000000000001</v>
       </c>
       <c r="F86">
-        <f>E86*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>141.24577097784413</v>
       </c>
     </row>
@@ -19568,11 +19567,11 @@
         <v>0.1321</v>
       </c>
       <c r="E87">
-        <f>AVERAGE(C87:D87)</f>
+        <f t="shared" si="6"/>
         <v>0.13155</v>
       </c>
       <c r="F87">
-        <f>E87*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>127.89853423030809</v>
       </c>
     </row>
@@ -19590,11 +19589,11 @@
         <v>3.1E-2</v>
       </c>
       <c r="E88">
-        <f>AVERAGE(C88:D88)</f>
+        <f t="shared" si="6"/>
         <v>2.9850000000000002E-2</v>
       </c>
       <c r="F88">
-        <f>E88*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>31.285439765936818</v>
       </c>
     </row>
@@ -19608,15 +19607,15 @@
       <c r="C89">
         <v>6.7400000000000002E-2</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="2">
         <v>6.3100000000000003E-2</v>
       </c>
       <c r="E89">
-        <f>AVERAGE(C89:D89)</f>
+        <f t="shared" si="6"/>
         <v>6.5250000000000002E-2</v>
       </c>
       <c r="F89">
-        <f>E89*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>64.914776482148653</v>
       </c>
     </row>
@@ -19630,15 +19629,15 @@
       <c r="C90">
         <v>5.57E-2</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90" s="2">
         <v>5.62E-2</v>
       </c>
       <c r="E90">
-        <f>AVERAGE(C90:D90)</f>
+        <f t="shared" si="6"/>
         <v>5.595E-2</v>
       </c>
       <c r="F90">
-        <f>E90*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>56.079950734669268</v>
       </c>
     </row>
@@ -19656,11 +19655,11 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="E91">
-        <f>AVERAGE(C91:D91)</f>
+        <f t="shared" si="6"/>
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="F91">
-        <f>E91*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>76.077056324394093</v>
       </c>
     </row>
@@ -19674,15 +19673,15 @@
       <c r="C92">
         <v>3.4599999999999999E-2</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="2">
         <v>3.1899999999999998E-2</v>
       </c>
       <c r="E92">
-        <f>AVERAGE(C92:D92)</f>
+        <f t="shared" si="6"/>
         <v>3.3250000000000002E-2</v>
       </c>
       <c r="F92">
-        <f>E92*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>34.515376060714225</v>
       </c>
     </row>
@@ -19700,11 +19699,11 @@
         <v>0.33090000000000003</v>
       </c>
       <c r="E93">
-        <f>AVERAGE(C93:D93)</f>
+        <f t="shared" si="6"/>
         <v>0.33579999999999999</v>
       </c>
       <c r="F93">
-        <f>E93*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>321.93220723274493</v>
       </c>
     </row>
@@ -19718,15 +19717,15 @@
       <c r="C94">
         <v>3.6700000000000003E-2</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="2">
         <v>3.5099999999999999E-2</v>
       </c>
       <c r="E94">
-        <f>AVERAGE(C94:D94)</f>
+        <f t="shared" si="6"/>
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F94">
-        <f>E94*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>37.032826408114261</v>
       </c>
     </row>
@@ -19744,11 +19743,11 @@
         <v>0.1056</v>
       </c>
       <c r="E95">
-        <f>AVERAGE(C95:D95)</f>
+        <f t="shared" si="6"/>
         <v>0.10719999999999999</v>
       </c>
       <c r="F95">
-        <f>E95*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>104.76649047212283</v>
       </c>
     </row>
@@ -19762,15 +19761,15 @@
       <c r="C96">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="2">
         <v>6.13E-2</v>
       </c>
       <c r="E96">
-        <f>AVERAGE(C96:D96)</f>
+        <f t="shared" si="6"/>
         <v>6.0149999999999995E-2</v>
       </c>
       <c r="F96">
-        <f>E96*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>60.069872039982528</v>
       </c>
     </row>
@@ -19788,11 +19787,11 @@
         <v>7.2900000000000006E-2</v>
       </c>
       <c r="E97">
-        <f>AVERAGE(C97:D97)</f>
+        <f t="shared" si="6"/>
         <v>7.17E-2</v>
       </c>
       <c r="F97">
-        <f>E97*$L$1+$L$2</f>
+        <f t="shared" si="5"/>
         <v>71.042155629594021</v>
       </c>
     </row>
@@ -19810,11 +19809,11 @@
         <v>0.11409999999999999</v>
       </c>
       <c r="E98">
-        <f>AVERAGE(C98:D98)</f>
+        <f t="shared" si="6"/>
         <v>0.11654999999999999</v>
       </c>
       <c r="F98">
-        <f>E98*$L$1+$L$2</f>
+        <f t="shared" ref="F98:F129" si="7">E98*$L$1+$L$2</f>
         <v>113.64881528276068</v>
       </c>
     </row>
@@ -19832,11 +19831,11 @@
         <v>0.04</v>
       </c>
       <c r="E99">
-        <f>AVERAGE(C99:D99)</f>
+        <f t="shared" si="6"/>
         <v>4.1999999999999996E-2</v>
       </c>
       <c r="F99">
-        <f>E99*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>42.82771211345019</v>
       </c>
     </row>
@@ -19850,15 +19849,15 @@
       <c r="C100">
         <v>0.20880000000000001</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="2">
         <v>0.22020000000000001</v>
       </c>
       <c r="E100">
-        <f>AVERAGE(C100:D100)</f>
+        <f t="shared" si="6"/>
         <v>0.21450000000000002</v>
       </c>
       <c r="F100">
-        <f>E100*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>206.69948001024517</v>
       </c>
     </row>
@@ -19876,11 +19875,11 @@
         <v>3.9800000000000002E-2</v>
       </c>
       <c r="E101">
-        <f>AVERAGE(C101:D101)</f>
+        <f t="shared" si="6"/>
         <v>4.1950000000000001E-2</v>
       </c>
       <c r="F101">
-        <f>E101*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>42.780213050291707</v>
       </c>
     </row>
@@ -19894,15 +19893,15 @@
       <c r="C102">
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="2">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="E102">
-        <f>AVERAGE(C102:D102)</f>
+        <f t="shared" si="6"/>
         <v>4.2399999999999993E-2</v>
       </c>
       <c r="F102">
-        <f>E102*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>43.207704618718118</v>
       </c>
     </row>
@@ -19916,15 +19915,15 @@
       <c r="C103">
         <v>4.0099999999999997E-2</v>
       </c>
-      <c r="D103" s="3">
+      <c r="D103" s="2">
         <v>3.85E-2</v>
       </c>
       <c r="E103">
-        <f>AVERAGE(C103:D103)</f>
+        <f t="shared" si="6"/>
         <v>3.9300000000000002E-2</v>
       </c>
       <c r="F103">
-        <f>E103*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>40.262762702891671</v>
       </c>
     </row>
@@ -19942,11 +19941,11 @@
         <v>7.9200000000000007E-2</v>
       </c>
       <c r="E104">
-        <f>AVERAGE(C104:D104)</f>
+        <f t="shared" si="6"/>
         <v>7.2300000000000003E-2</v>
       </c>
       <c r="F104">
-        <f>E104*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>71.612144387495917</v>
       </c>
     </row>
@@ -19960,15 +19959,15 @@
       <c r="C105">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="D105" s="3">
+      <c r="D105" s="2">
         <v>3.61E-2</v>
       </c>
       <c r="E105">
-        <f>AVERAGE(C105:D105)</f>
+        <f t="shared" si="6"/>
         <v>3.4549999999999997E-2</v>
       </c>
       <c r="F105">
-        <f>E105*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>35.75035170283499</v>
       </c>
     </row>
@@ -19982,15 +19981,15 @@
       <c r="C106">
         <v>2.2800000000000001E-2</v>
       </c>
-      <c r="D106" s="3">
+      <c r="D106" s="2">
         <v>2.75E-2</v>
       </c>
       <c r="E106">
-        <f>AVERAGE(C106:D106)</f>
+        <f t="shared" si="6"/>
         <v>2.5149999999999999E-2</v>
       </c>
       <c r="F106">
-        <f>E106*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>26.820527829038635</v>
       </c>
     </row>
@@ -20008,11 +20007,11 @@
         <v>4.6199999999999998E-2</v>
       </c>
       <c r="E107">
-        <f>AVERAGE(C107:D107)</f>
+        <f t="shared" si="6"/>
         <v>4.4299999999999999E-2</v>
       </c>
       <c r="F107">
-        <f>E107*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>45.012669018740795</v>
       </c>
     </row>
@@ -20030,11 +20029,11 @@
         <v>2.8500000000000001E-2</v>
       </c>
       <c r="E108">
-        <f>AVERAGE(C108:D108)</f>
+        <f t="shared" si="6"/>
         <v>2.9400000000000003E-2</v>
       </c>
       <c r="F108">
-        <f>E108*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>30.857948197510396</v>
       </c>
     </row>
@@ -20048,15 +20047,15 @@
       <c r="C109">
         <v>5.3E-3</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D109" s="2">
         <v>1.4200000000000001E-2</v>
       </c>
       <c r="E109">
-        <f>AVERAGE(C109:D109)</f>
+        <f t="shared" si="6"/>
         <v>9.75E-3</v>
       </c>
       <c r="F109">
-        <f>E109*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>12.190816376223321</v>
       </c>
     </row>
@@ -20070,15 +20069,15 @@
       <c r="C110">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D110" s="2">
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="E110">
-        <f>AVERAGE(C110:D110)</f>
+        <f t="shared" si="6"/>
         <v>1.3500000000000002E-2</v>
       </c>
       <c r="F110">
-        <f>E110*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>15.753246113110167</v>
       </c>
     </row>
@@ -20092,15 +20091,15 @@
       <c r="C111">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="D111" s="3">
+      <c r="D111" s="2">
         <v>1.14E-2</v>
       </c>
       <c r="E111">
-        <f>AVERAGE(C111:D111)</f>
+        <f t="shared" si="6"/>
         <v>1.0950000000000001E-2</v>
       </c>
       <c r="F111">
-        <f>E111*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>13.330793892027112</v>
       </c>
     </row>
@@ -20118,11 +20117,11 @@
         <v>2.18E-2</v>
       </c>
       <c r="E112">
-        <f>AVERAGE(C112:D112)</f>
+        <f t="shared" si="6"/>
         <v>2.605E-2</v>
       </c>
       <c r="F112">
-        <f>E112*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>27.67551096589148</v>
       </c>
     </row>
@@ -20140,11 +20139,11 @@
         <v>1.29E-2</v>
       </c>
       <c r="E113">
-        <f>AVERAGE(C113:D113)</f>
+        <f t="shared" si="6"/>
         <v>1.145E-2</v>
       </c>
       <c r="F113">
-        <f>E113*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>13.805784523612024</v>
       </c>
     </row>
@@ -20158,7 +20157,7 @@
       <c r="C114">
         <v>9.5999999999999992E-3</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="1">
         <v>5.4199999999999998E-2</v>
       </c>
       <c r="E114">
@@ -20166,7 +20165,7 @@
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="F114">
-        <f>E114*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>12.048319186747845</v>
       </c>
     </row>
@@ -20180,7 +20179,7 @@
       <c r="C115">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="D115" s="3">
+      <c r="D115" s="2">
         <v>9.7000000000000003E-3</v>
       </c>
       <c r="E115">
@@ -20188,7 +20187,7 @@
         <v>1.0200000000000001E-2</v>
       </c>
       <c r="F115">
-        <f>E115*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>12.618307944649743</v>
       </c>
     </row>
@@ -20210,7 +20209,7 @@
         <v>1.7349999999999997E-2</v>
       </c>
       <c r="F116">
-        <f>E116*$L$1+$L$2</f>
+        <f t="shared" si="7"/>
         <v>19.410673976313994</v>
       </c>
     </row>
